--- a/data/trans_camb/P19C01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -1,49</t>
+          <t>-10,04; -2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 9,52</t>
+          <t>-1,01; 9,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 19,35</t>
+          <t>8,72; 19,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,39</t>
+          <t>-3,52; 4,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,26</t>
+          <t>6,71; 16,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 22,5</t>
+          <t>14,6; 22,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,83</t>
+          <t>-5,05; 0,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 11,99</t>
+          <t>4,84; 11,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,68; 19,95</t>
+          <t>13,44; 19,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; -6,84</t>
+          <t>-39,28; -9,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 45,74</t>
+          <t>-3,93; 47,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,52; 93,9</t>
+          <t>34,59; 93,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 21,8</t>
+          <t>-14,15; 21,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,71; 77,24</t>
+          <t>28,0; 79,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,3; 109,9</t>
+          <t>58,17; 109,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 3,59</t>
+          <t>-20,9; 2,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 56,24</t>
+          <t>19,78; 55,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,91; 93,33</t>
+          <t>55,7; 93,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,03</t>
+          <t>-1,65; 5,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 15,54</t>
+          <t>8,53; 15,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 30,69</t>
+          <t>7,53; 30,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,06</t>
+          <t>-2,68; 4,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,58</t>
+          <t>5,53; 12,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 29,57</t>
+          <t>3,26; 29,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,2</t>
+          <t>-0,84; 3,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,86</t>
+          <t>7,96; 12,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 29,12</t>
+          <t>11,3; 28,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 18,56</t>
+          <t>-5,12; 18,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 56,68</t>
+          <t>27,05; 55,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 106,52</t>
+          <t>26,44; 107,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 15,07</t>
+          <t>-7,02; 14,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 37,66</t>
+          <t>14,88; 37,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 84,8</t>
+          <t>9,22; 85,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 13,5</t>
+          <t>-2,52; 12,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,73; 41,04</t>
+          <t>23,61; 41,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,57; 91,21</t>
+          <t>34,26; 89,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 9,79</t>
+          <t>-3,93; 10,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 16,76</t>
+          <t>3,9; 17,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 34,17</t>
+          <t>22,11; 34,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 22,54</t>
+          <t>8,89; 23,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 19,78</t>
+          <t>6,08; 19,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,53; 33,65</t>
+          <t>22,47; 34,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 14,2</t>
+          <t>3,95; 13,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 16,05</t>
+          <t>6,97; 16,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,43; 32,41</t>
+          <t>24,02; 32,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 26,92</t>
+          <t>-9,1; 27,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 44,9</t>
+          <t>8,72; 46,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,08; 93,59</t>
+          <t>50,36; 96,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,56; 62,55</t>
+          <t>21,76; 66,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 54,31</t>
+          <t>14,09; 54,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,78; 96,62</t>
+          <t>50,56; 97,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 38,13</t>
+          <t>9,04; 37,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,21; 43,2</t>
+          <t>16,54; 43,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54,13; 87,28</t>
+          <t>55,76; 87,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,03</t>
+          <t>-2,73; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,42</t>
+          <t>8,34; 13,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,85; 28,63</t>
+          <t>8,93; 28,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,51</t>
+          <t>0,4; 5,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 15,02</t>
+          <t>9,33; 14,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,93; 28,9</t>
+          <t>12,99; 28,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,96</t>
+          <t>-0,46; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,45</t>
+          <t>9,69; 13,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,89; 27,88</t>
+          <t>17,31; 27,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 7,24</t>
+          <t>-8,76; 7,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,62; 47,2</t>
+          <t>26,45; 48,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,89; 98,61</t>
+          <t>37,08; 98,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 18,37</t>
+          <t>1,27; 18,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,78; 50,37</t>
+          <t>27,77; 48,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,68; 93,71</t>
+          <t>44,69; 94,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,95</t>
+          <t>-1,44; 9,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,7; 45,4</t>
+          <t>30,83; 45,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,38; 92,12</t>
+          <t>55,56; 92,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>13,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>19,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,77</t>
+          <t>17,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -2,06</t>
+          <t>-10,06; -1,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 9,81</t>
+          <t>-1,02; 8,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 19,45</t>
+          <t>8,26; 19,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 4,32</t>
+          <t>-3,09; 4,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 16,46</t>
+          <t>6,93; 15,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 22,52</t>
+          <t>15,6; 23,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 0,52</t>
+          <t>-4,58; 1,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,97</t>
+          <t>4,95; 11,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,44; 19,85</t>
+          <t>13,95; 20,09</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -9,37</t>
+          <t>-39,4; -8,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 47,04</t>
+          <t>-4,02; 42,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,59; 93,37</t>
+          <t>31,19; 89,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 21,23</t>
+          <t>-11,91; 21,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 79,34</t>
+          <t>29,7; 79,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,17; 109,89</t>
+          <t>63,65; 116,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 2,46</t>
+          <t>-18,97; 4,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 55,0</t>
+          <t>20,08; 55,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,7; 93,91</t>
+          <t>57,72; 95,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,91</t>
+          <t>28,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,94</t>
+          <t>27,41</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22,34</t>
+          <t>28,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,11</t>
+          <t>-2,04; 4,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 15,35</t>
+          <t>8,57; 15,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 30,92</t>
+          <t>25,42; 31,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,87</t>
+          <t>-2,07; 4,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 12,51</t>
+          <t>5,56; 12,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 29,39</t>
+          <t>24,11; 30,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,97</t>
+          <t>-0,93; 4,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,97</t>
+          <t>7,9; 12,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 28,63</t>
+          <t>25,64; 30,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 18,53</t>
+          <t>-6,46; 17,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,05; 55,91</t>
+          <t>26,78; 55,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 107,48</t>
+          <t>80,81; 116,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 14,61</t>
+          <t>-5,59; 14,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,88; 37,0</t>
+          <t>14,75; 37,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 85,22</t>
+          <t>63,91; 91,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 12,69</t>
+          <t>-2,81; 12,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 41,53</t>
+          <t>23,47; 41,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,26; 89,58</t>
+          <t>75,35; 99,13</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28,37</t>
+          <t>28,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,33</t>
+          <t>28,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28,31</t>
+          <t>28,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 10,16</t>
+          <t>-4,83; 8,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 17,18</t>
+          <t>3,41; 17,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,11; 34,9</t>
+          <t>21,54; 34,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 23,49</t>
+          <t>7,97; 22,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 19,24</t>
+          <t>6,26; 19,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,47; 34,59</t>
+          <t>21,88; 34,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,9</t>
+          <t>4,21; 14,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 16,35</t>
+          <t>6,65; 15,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,02; 32,65</t>
+          <t>23,83; 32,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 27,68</t>
+          <t>-10,92; 24,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,72; 46,01</t>
+          <t>7,35; 45,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50,36; 96,82</t>
+          <t>48,8; 93,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,76; 66,73</t>
+          <t>18,68; 62,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 54,48</t>
+          <t>14,68; 57,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,56; 97,89</t>
+          <t>50,78; 96,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,04; 37,15</t>
+          <t>10,28; 37,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 43,93</t>
+          <t>15,88; 42,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55,76; 87,13</t>
+          <t>55,93; 87,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23,55</t>
+          <t>27,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,48</t>
+          <t>27,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24,01</t>
+          <t>27,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,18</t>
+          <t>-2,96; 2,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 13,78</t>
+          <t>8,36; 13,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 28,53</t>
+          <t>24,37; 29,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,51</t>
+          <t>0,49; 5,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 14,69</t>
+          <t>9,39; 14,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,99; 28,92</t>
+          <t>25,49; 29,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,92</t>
+          <t>-0,45; 3,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,69; 13,42</t>
+          <t>9,55; 13,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,31; 27,72</t>
+          <t>25,65; 29,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 7,66</t>
+          <t>-9,53; 7,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,45; 48,87</t>
+          <t>26,76; 48,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,08; 98,22</t>
+          <t>77,22; 105,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 18,23</t>
+          <t>1,48; 17,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,77; 48,45</t>
+          <t>28,91; 48,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,69; 94,09</t>
+          <t>77,65; 99,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 9,92</t>
+          <t>-1,4; 10,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,83; 45,38</t>
+          <t>30,05; 44,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,56; 92,08</t>
+          <t>81,08; 99,66</t>
         </is>
       </c>
     </row>
